--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/32.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/32.xlsx
@@ -426,13 +426,13 @@
         <v>-20.21556753743132</v>
       </c>
       <c r="E2">
-        <v>-10.18389697022002</v>
+        <v>-6.544167927536657</v>
       </c>
       <c r="F2">
-        <v>3.374999766263059</v>
+        <v>2.40997990649333</v>
       </c>
       <c r="G2">
-        <v>-16.67691114419977</v>
+        <v>-14.45694541422892</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.94016146602853</v>
       </c>
       <c r="E3">
-        <v>-9.027310680481769</v>
+        <v>-7.136058686283271</v>
       </c>
       <c r="F3">
-        <v>3.115232032419162</v>
+        <v>2.564226887099015</v>
       </c>
       <c r="G3">
-        <v>-15.33442319816357</v>
+        <v>-13.36307867560443</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.37212409222872</v>
       </c>
       <c r="E4">
-        <v>-12.63730688329069</v>
+        <v>-6.6745330778117</v>
       </c>
       <c r="F4">
-        <v>3.007474687193391</v>
+        <v>2.484219849867028</v>
       </c>
       <c r="G4">
-        <v>-16.08807075539713</v>
+        <v>-13.07558087048644</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.52906501870797</v>
       </c>
       <c r="E5">
-        <v>-11.25941257489762</v>
+        <v>-8.25556925852478</v>
       </c>
       <c r="F5">
-        <v>3.255098554912248</v>
+        <v>2.848211113596353</v>
       </c>
       <c r="G5">
-        <v>-15.26924857019102</v>
+        <v>-13.01468394752643</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.42754501381909</v>
       </c>
       <c r="E6">
-        <v>-12.65161884951605</v>
+        <v>-9.262851754346771</v>
       </c>
       <c r="F6">
-        <v>3.469895879192965</v>
+        <v>2.723704179485976</v>
       </c>
       <c r="G6">
-        <v>-14.20233907484207</v>
+        <v>-12.0839939673357</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.12018953038642</v>
       </c>
       <c r="E7">
-        <v>-12.16176418659782</v>
+        <v>-9.84820951167943</v>
       </c>
       <c r="F7">
-        <v>3.293064289717354</v>
+        <v>2.865214182906215</v>
       </c>
       <c r="G7">
-        <v>-14.3550663280499</v>
+        <v>-11.77167581339</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.66802949326024</v>
       </c>
       <c r="E8">
-        <v>-14.39202620839677</v>
+        <v>-10.35128799945591</v>
       </c>
       <c r="F8">
-        <v>3.212495619386269</v>
+        <v>3.137700669852696</v>
       </c>
       <c r="G8">
-        <v>-13.61847345985779</v>
+        <v>-10.50047816453104</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.12996506592802</v>
       </c>
       <c r="E9">
-        <v>-14.13674076789354</v>
+        <v>-10.90334946159742</v>
       </c>
       <c r="F9">
-        <v>3.167528523292701</v>
+        <v>3.349886980079789</v>
       </c>
       <c r="G9">
-        <v>-12.53198729619238</v>
+        <v>-10.32636891312199</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.57406302147805</v>
       </c>
       <c r="E10">
-        <v>-14.2853094434053</v>
+        <v>-11.89658994993017</v>
       </c>
       <c r="F10">
-        <v>3.616912869107016</v>
+        <v>3.228058986150066</v>
       </c>
       <c r="G10">
-        <v>-11.81059679375432</v>
+        <v>-9.882722474009514</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.04047171967175</v>
       </c>
       <c r="E11">
-        <v>-15.16561996260464</v>
+        <v>-12.47748715829996</v>
       </c>
       <c r="F11">
-        <v>3.226208413372212</v>
+        <v>3.177232019049094</v>
       </c>
       <c r="G11">
-        <v>-11.76707045993128</v>
+        <v>-9.185145878359295</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.587282073114876</v>
       </c>
       <c r="E12">
-        <v>-16.11138924549459</v>
+        <v>-13.24660375069966</v>
       </c>
       <c r="F12">
-        <v>4.089577652409607</v>
+        <v>3.651964407389074</v>
       </c>
       <c r="G12">
-        <v>-11.65791914469372</v>
+        <v>-8.233490313729636</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.235016322422552</v>
       </c>
       <c r="E13">
-        <v>-16.40543245408113</v>
+        <v>-14.12696410843489</v>
       </c>
       <c r="F13">
-        <v>4.278647541894178</v>
+        <v>3.650720199550069</v>
       </c>
       <c r="G13">
-        <v>-9.517658141717256</v>
+        <v>-8.457821153465636</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.027265466949681</v>
       </c>
       <c r="E14">
-        <v>-18.09229245935084</v>
+        <v>-14.83360809608652</v>
       </c>
       <c r="F14">
-        <v>4.643435695064997</v>
+        <v>3.852563514385808</v>
       </c>
       <c r="G14">
-        <v>-10.94133763379249</v>
+        <v>-7.043721788667489</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.971899937909185</v>
       </c>
       <c r="E15">
-        <v>-19.62023398648731</v>
+        <v>-15.49952569348688</v>
       </c>
       <c r="F15">
-        <v>4.201935750190527</v>
+        <v>3.675006275065345</v>
       </c>
       <c r="G15">
-        <v>-9.271564135069736</v>
+        <v>-6.872266359135306</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.083822761405115</v>
       </c>
       <c r="E16">
-        <v>-19.29419859106562</v>
+        <v>-15.89549701440735</v>
       </c>
       <c r="F16">
-        <v>5.099241544985813</v>
+        <v>4.210332082185303</v>
       </c>
       <c r="G16">
-        <v>-9.759696356642483</v>
+        <v>-5.987417137847645</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.356301652260463</v>
       </c>
       <c r="E17">
-        <v>-18.73282147592252</v>
+        <v>-16.90427466630628</v>
       </c>
       <c r="F17">
-        <v>4.640481736906613</v>
+        <v>4.319096722172878</v>
       </c>
       <c r="G17">
-        <v>-8.371408118244377</v>
+        <v>-5.580592640448235</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.777701326599335</v>
       </c>
       <c r="E18">
-        <v>-22.56782205546535</v>
+        <v>-17.62072853910716</v>
       </c>
       <c r="F18">
-        <v>5.377533230691113</v>
+        <v>4.592593817350774</v>
       </c>
       <c r="G18">
-        <v>-7.576817558960684</v>
+        <v>-4.829593683602361</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.331164666163827</v>
       </c>
       <c r="E19">
-        <v>-20.76640817543421</v>
+        <v>-18.76240480018927</v>
       </c>
       <c r="F19">
-        <v>5.453506118671466</v>
+        <v>4.657373804984501</v>
       </c>
       <c r="G19">
-        <v>-6.826839403249935</v>
+        <v>-4.312272032128671</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.987439012032165</v>
       </c>
       <c r="E20">
-        <v>-20.94091780888086</v>
+        <v>-19.53036264662934</v>
       </c>
       <c r="F20">
-        <v>6.090895073490352</v>
+        <v>5.03539761251725</v>
       </c>
       <c r="G20">
-        <v>-6.701220816503928</v>
+        <v>-4.104542917247561</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.723221328841229</v>
       </c>
       <c r="E21">
-        <v>-21.88851865796507</v>
+        <v>-19.94759425632162</v>
       </c>
       <c r="F21">
-        <v>5.24775456642932</v>
+        <v>4.870741367127986</v>
       </c>
       <c r="G21">
-        <v>-6.423359269671741</v>
+        <v>-4.152222945715063</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.507034643612716</v>
       </c>
       <c r="E22">
-        <v>-21.68137308992792</v>
+        <v>-19.50920203492934</v>
       </c>
       <c r="F22">
-        <v>6.237933600956875</v>
+        <v>4.972840962992636</v>
       </c>
       <c r="G22">
-        <v>-6.772666452984335</v>
+        <v>-3.906692859899223</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.326311429964874</v>
       </c>
       <c r="E23">
-        <v>-22.97038036954701</v>
+        <v>-19.8687040072065</v>
       </c>
       <c r="F23">
-        <v>6.481286406346897</v>
+        <v>5.249891754328543</v>
       </c>
       <c r="G23">
-        <v>-5.927620643732786</v>
+        <v>-3.379648795568228</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.164137664002156</v>
       </c>
       <c r="E24">
-        <v>-22.94200562977577</v>
+        <v>-20.98617535268752</v>
       </c>
       <c r="F24">
-        <v>5.920957157540839</v>
+        <v>5.5132579161702</v>
       </c>
       <c r="G24">
-        <v>-6.156760475005617</v>
+        <v>-3.499414092940959</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.022822234593642</v>
       </c>
       <c r="E25">
-        <v>-24.28330599318578</v>
+        <v>-21.45476557362262</v>
       </c>
       <c r="F25">
-        <v>6.613208885447135</v>
+        <v>5.087581445424007</v>
       </c>
       <c r="G25">
-        <v>-5.916598080069106</v>
+        <v>-3.557168984785567</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9011775989597667</v>
       </c>
       <c r="E26">
-        <v>-23.75778355140992</v>
+        <v>-21.83244615186856</v>
       </c>
       <c r="F26">
-        <v>6.160191320204142</v>
+        <v>5.39528017392869</v>
       </c>
       <c r="G26">
-        <v>-7.153631525208767</v>
+        <v>-3.509037297503803</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.8073336300658209</v>
       </c>
       <c r="E27">
-        <v>-21.66826140177544</v>
+        <v>-21.25686505399454</v>
       </c>
       <c r="F27">
-        <v>6.371849132028249</v>
+        <v>5.216795163117091</v>
       </c>
       <c r="G27">
-        <v>-7.513439123266818</v>
+        <v>-3.526458796160302</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.7444712518311289</v>
       </c>
       <c r="E28">
-        <v>-22.40393218337629</v>
+        <v>-21.38536125917341</v>
       </c>
       <c r="F28">
-        <v>5.485535772668112</v>
+        <v>5.221760397329471</v>
       </c>
       <c r="G28">
-        <v>-6.926964069063721</v>
+        <v>-3.891882105833837</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7152498501497638</v>
       </c>
       <c r="E29">
-        <v>-23.54635602249688</v>
+        <v>-21.42553111910716</v>
       </c>
       <c r="F29">
-        <v>6.402810192075283</v>
+        <v>5.159828336826569</v>
       </c>
       <c r="G29">
-        <v>-7.315134796359626</v>
+        <v>-4.123844152009661</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7173773920715468</v>
       </c>
       <c r="E30">
-        <v>-22.34616101384792</v>
+        <v>-21.36277609598899</v>
       </c>
       <c r="F30">
-        <v>6.127605003312815</v>
+        <v>5.065777158647519</v>
       </c>
       <c r="G30">
-        <v>-7.518822478613694</v>
+        <v>-3.7059004933967</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.7468151676071872</v>
       </c>
       <c r="E31">
-        <v>-21.49263870769374</v>
+        <v>-21.83234232158544</v>
       </c>
       <c r="F31">
-        <v>6.236041609808881</v>
+        <v>5.19842860106222</v>
       </c>
       <c r="G31">
-        <v>-7.802597361944752</v>
+        <v>-4.072981625885593</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7985970826586744</v>
       </c>
       <c r="E32">
-        <v>-22.74416740831757</v>
+        <v>-21.14741547595134</v>
       </c>
       <c r="F32">
-        <v>5.947867500988184</v>
+        <v>5.131281139391293</v>
       </c>
       <c r="G32">
-        <v>-6.021628334969593</v>
+        <v>-4.144502973959141</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8670848134941526</v>
       </c>
       <c r="E33">
-        <v>-22.43038398630412</v>
+        <v>-20.67921150366944</v>
       </c>
       <c r="F33">
-        <v>5.835123383997559</v>
+        <v>5.237325420828074</v>
       </c>
       <c r="G33">
-        <v>-7.246276407769013</v>
+        <v>-4.182839147535049</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9491645566377631</v>
       </c>
       <c r="E34">
-        <v>-22.78617298765688</v>
+        <v>-20.55010892963714</v>
       </c>
       <c r="F34">
-        <v>6.980828398400722</v>
+        <v>5.442159141987919</v>
       </c>
       <c r="G34">
-        <v>-6.608320080973753</v>
+        <v>-4.48341156156533</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.040911866757133</v>
       </c>
       <c r="E35">
-        <v>-20.73851936138799</v>
+        <v>-19.82168134858679</v>
       </c>
       <c r="F35">
-        <v>6.717275025526032</v>
+        <v>5.683611672555919</v>
       </c>
       <c r="G35">
-        <v>-7.881768191670263</v>
+        <v>-4.699006849899465</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.142577817891046</v>
       </c>
       <c r="E36">
-        <v>-22.31994179075428</v>
+        <v>-19.76654746824969</v>
       </c>
       <c r="F36">
-        <v>6.744259922039628</v>
+        <v>5.37849413687836</v>
       </c>
       <c r="G36">
-        <v>-8.427841973325881</v>
+        <v>-4.69381407890774</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.25168448609013</v>
       </c>
       <c r="E37">
-        <v>-20.72908326525798</v>
+        <v>-18.9410427256928</v>
       </c>
       <c r="F37">
-        <v>6.24880343801641</v>
+        <v>5.810920145222564</v>
       </c>
       <c r="G37">
-        <v>-7.521600310858638</v>
+        <v>-4.881879065528586</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.369238582734753</v>
       </c>
       <c r="E38">
-        <v>-21.04424555343127</v>
+        <v>-19.08790443135006</v>
       </c>
       <c r="F38">
-        <v>6.450626872034482</v>
+        <v>5.435601785627358</v>
       </c>
       <c r="G38">
-        <v>-7.76394528827332</v>
+        <v>-4.527073654107109</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.492002433525527</v>
       </c>
       <c r="E39">
-        <v>-20.35529839923474</v>
+        <v>-18.76564430502264</v>
       </c>
       <c r="F39">
-        <v>7.362818429058075</v>
+        <v>5.694281044703977</v>
       </c>
       <c r="G39">
-        <v>-8.221816369290472</v>
+        <v>-4.378890401860109</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.619215843372306</v>
       </c>
       <c r="E40">
-        <v>-19.27292999587117</v>
+        <v>-18.5437963688956</v>
       </c>
       <c r="F40">
-        <v>6.665294971000363</v>
+        <v>6.108961766545409</v>
       </c>
       <c r="G40">
-        <v>-8.180672339906822</v>
+        <v>-5.004320376107208</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.745718636025398</v>
       </c>
       <c r="E41">
-        <v>-20.25695866148545</v>
+        <v>-17.10817242308741</v>
       </c>
       <c r="F41">
-        <v>6.73530361368056</v>
+        <v>6.153566037716551</v>
       </c>
       <c r="G41">
-        <v>-8.818372813732154</v>
+        <v>-4.933819829168785</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.867227509261778</v>
       </c>
       <c r="E42">
-        <v>-18.88617049766916</v>
+        <v>-17.87915796058329</v>
       </c>
       <c r="F42">
-        <v>6.786264776300786</v>
+        <v>6.062781940574142</v>
       </c>
       <c r="G42">
-        <v>-8.350566544173519</v>
+        <v>-4.90951379702552</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.977555030270776</v>
       </c>
       <c r="E43">
-        <v>-19.25911641500479</v>
+        <v>-16.72779225748034</v>
       </c>
       <c r="F43">
-        <v>6.335490429984573</v>
+        <v>5.958321497611514</v>
       </c>
       <c r="G43">
-        <v>-8.381535196513305</v>
+        <v>-5.496482281956338</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.072500854059561</v>
       </c>
       <c r="E44">
-        <v>-19.02435614486886</v>
+        <v>-15.67333758743095</v>
       </c>
       <c r="F44">
-        <v>6.508768323302173</v>
+        <v>5.84415424542288</v>
       </c>
       <c r="G44">
-        <v>-8.85529918522886</v>
+        <v>-5.626426872489819</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.150778273105364</v>
       </c>
       <c r="E45">
-        <v>-16.87545968613462</v>
+        <v>-15.96182379926486</v>
       </c>
       <c r="F45">
-        <v>6.332579546931136</v>
+        <v>5.701675052141365</v>
       </c>
       <c r="G45">
-        <v>-8.834483718603915</v>
+        <v>-5.748118899370792</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.212578304907993</v>
       </c>
       <c r="E46">
-        <v>-18.21700093580147</v>
+        <v>-15.73076819363068</v>
       </c>
       <c r="F46">
-        <v>6.306230836582889</v>
+        <v>5.598157291283122</v>
       </c>
       <c r="G46">
-        <v>-9.115125708425637</v>
+        <v>-5.462002178141505</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.264277812833238</v>
       </c>
       <c r="E47">
-        <v>-16.75234604283273</v>
+        <v>-14.37165886005981</v>
       </c>
       <c r="F47">
-        <v>6.664743278310098</v>
+        <v>6.058027111682073</v>
       </c>
       <c r="G47">
-        <v>-9.418096091362855</v>
+        <v>-5.978827788142882</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.310378737438745</v>
       </c>
       <c r="E48">
-        <v>-15.35279689059201</v>
+        <v>-14.62004996976383</v>
       </c>
       <c r="F48">
-        <v>6.380435988525669</v>
+        <v>5.997132167167476</v>
       </c>
       <c r="G48">
-        <v>-8.978166047175833</v>
+        <v>-5.187453666195441</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.362893109317606</v>
       </c>
       <c r="E49">
-        <v>-16.12851708899818</v>
+        <v>-13.73245056468943</v>
       </c>
       <c r="F49">
-        <v>6.009731635364056</v>
+        <v>6.032601202620545</v>
       </c>
       <c r="G49">
-        <v>-9.059707432990075</v>
+        <v>-5.66610757953015</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.427749111332425</v>
       </c>
       <c r="E50">
-        <v>-16.03086678432881</v>
+        <v>-13.19464292381473</v>
       </c>
       <c r="F50">
-        <v>6.193509913879543</v>
+        <v>5.783353734792202</v>
       </c>
       <c r="G50">
-        <v>-9.120250600057991</v>
+        <v>-6.104232293832418</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.51783897685468</v>
       </c>
       <c r="E51">
-        <v>-16.47813857153357</v>
+        <v>-12.85397576489567</v>
       </c>
       <c r="F51">
-        <v>6.461533157259741</v>
+        <v>5.642614113056566</v>
       </c>
       <c r="G51">
-        <v>-8.513265536347109</v>
+        <v>-6.344566997911942</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.638803684492512</v>
       </c>
       <c r="E52">
-        <v>-14.92385737817504</v>
+        <v>-12.84361350264022</v>
       </c>
       <c r="F52">
-        <v>6.038553850777062</v>
+        <v>5.626427814005863</v>
       </c>
       <c r="G52">
-        <v>-9.114727569875491</v>
+        <v>-6.567725613326533</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.799631552950646</v>
       </c>
       <c r="E53">
-        <v>-13.4205443941948</v>
+        <v>-11.92356921069625</v>
       </c>
       <c r="F53">
-        <v>6.286911652014799</v>
+        <v>5.67523522137881</v>
       </c>
       <c r="G53">
-        <v>-8.519060083967085</v>
+        <v>-6.285744311529569</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.003169790942214</v>
       </c>
       <c r="E54">
-        <v>-14.16281047537948</v>
+        <v>-12.09329019148537</v>
       </c>
       <c r="F54">
-        <v>6.500219571705283</v>
+        <v>5.559618326235277</v>
       </c>
       <c r="G54">
-        <v>-9.034811372569219</v>
+        <v>-6.425484415768907</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.250640758124342</v>
       </c>
       <c r="E55">
-        <v>-14.57475504705525</v>
+        <v>-12.18170375416832</v>
       </c>
       <c r="F55">
-        <v>5.824929494738709</v>
+        <v>5.688159409597288</v>
       </c>
       <c r="G55">
-        <v>-8.926605146873642</v>
+        <v>-6.802434162812208</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.540146168651344</v>
       </c>
       <c r="E56">
-        <v>-11.66955880606974</v>
+        <v>-10.57335190257184</v>
       </c>
       <c r="F56">
-        <v>6.17347667661024</v>
+        <v>5.46883754256248</v>
       </c>
       <c r="G56">
-        <v>-9.181041787862064</v>
+        <v>-6.810430873494788</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.863696888498833</v>
       </c>
       <c r="E57">
-        <v>-13.53338714589039</v>
+        <v>-11.22331286206221</v>
       </c>
       <c r="F57">
-        <v>6.081771434915918</v>
+        <v>5.560658755693194</v>
       </c>
       <c r="G57">
-        <v>-9.272035374468432</v>
+        <v>-7.229776501953177</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.216706807528755</v>
       </c>
       <c r="E58">
-        <v>-14.48284032722547</v>
+        <v>-10.10605748357009</v>
       </c>
       <c r="F58">
-        <v>6.251825322301823</v>
+        <v>5.596752380167974</v>
       </c>
       <c r="G58">
-        <v>-9.712187331945698</v>
+        <v>-7.181326303831297</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.584855462423121</v>
       </c>
       <c r="E59">
-        <v>-12.73398948972137</v>
+        <v>-10.22620573398605</v>
       </c>
       <c r="F59">
-        <v>5.952870840101093</v>
+        <v>5.268795098460427</v>
       </c>
       <c r="G59">
-        <v>-9.918434849271353</v>
+        <v>-7.627972488478957</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.964179685038419</v>
       </c>
       <c r="E60">
-        <v>-11.37612196633663</v>
+        <v>-9.640033947233723</v>
       </c>
       <c r="F60">
-        <v>5.818618991864183</v>
+        <v>5.244401335182787</v>
       </c>
       <c r="G60">
-        <v>-10.19818396444292</v>
+        <v>-7.305929310931361</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.339085256768043</v>
       </c>
       <c r="E61">
-        <v>-12.78591293770438</v>
+        <v>-9.581830843727577</v>
       </c>
       <c r="F61">
-        <v>6.114528395492222</v>
+        <v>5.733804110226346</v>
       </c>
       <c r="G61">
-        <v>-9.627456921613412</v>
+        <v>-8.1373757516078</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.708338718348953</v>
       </c>
       <c r="E62">
-        <v>-11.80065907474928</v>
+        <v>-9.431384916696988</v>
       </c>
       <c r="F62">
-        <v>5.681688203446618</v>
+        <v>5.295140495339063</v>
       </c>
       <c r="G62">
-        <v>-9.532729970241753</v>
+        <v>-7.88209192399956</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.061676978451773</v>
       </c>
       <c r="E63">
-        <v>-11.2737453071796</v>
+        <v>-8.886973669815813</v>
       </c>
       <c r="F63">
-        <v>4.922272446521339</v>
+        <v>5.419958895592893</v>
       </c>
       <c r="G63">
-        <v>-10.84944334030219</v>
+        <v>-7.963541933753113</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.400034467886182</v>
       </c>
       <c r="E64">
-        <v>-11.79020959505601</v>
+        <v>-8.593902312679287</v>
       </c>
       <c r="F64">
-        <v>5.904071716402174</v>
+        <v>5.673923087412776</v>
       </c>
       <c r="G64">
-        <v>-9.899649236565997</v>
+        <v>-7.915499011787446</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.719689436267966</v>
       </c>
       <c r="E65">
-        <v>-13.48095285291443</v>
+        <v>-8.638474576617346</v>
       </c>
       <c r="F65">
-        <v>5.902969987756451</v>
+        <v>5.116865889847776</v>
       </c>
       <c r="G65">
-        <v>-10.42518298515103</v>
+        <v>-8.268401190402002</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.021626852631528</v>
       </c>
       <c r="E66">
-        <v>-13.26828766702659</v>
+        <v>-8.600111363609905</v>
       </c>
       <c r="F66">
-        <v>5.372847984660879</v>
+        <v>5.173834372873103</v>
       </c>
       <c r="G66">
-        <v>-10.45047979486662</v>
+        <v>-8.564376083207334</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.307838857447831</v>
       </c>
       <c r="E67">
-        <v>-12.61399906133575</v>
+        <v>-8.589504061886293</v>
       </c>
       <c r="F67">
-        <v>5.627796276955288</v>
+        <v>5.077347794529822</v>
       </c>
       <c r="G67">
-        <v>-10.09543288957047</v>
+        <v>-8.284707901118097</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.576784046909836</v>
       </c>
       <c r="E68">
-        <v>-10.84894239324217</v>
+        <v>-8.126333781730089</v>
       </c>
       <c r="F68">
-        <v>5.517439514819532</v>
+        <v>5.301366504738504</v>
       </c>
       <c r="G68">
-        <v>-9.885183100786637</v>
+        <v>-8.305860153795296</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.834861118220863</v>
       </c>
       <c r="E69">
-        <v>-11.15890070762545</v>
+        <v>-8.460546850250367</v>
       </c>
       <c r="F69">
-        <v>5.981320290182839</v>
+        <v>5.165176276779043</v>
       </c>
       <c r="G69">
-        <v>-9.81971345867529</v>
+        <v>-8.253440318522628</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.076539776709863</v>
       </c>
       <c r="E70">
-        <v>-12.75441082980555</v>
+        <v>-8.63996557948296</v>
       </c>
       <c r="F70">
-        <v>5.182540514276526</v>
+        <v>5.178744934836899</v>
       </c>
       <c r="G70">
-        <v>-11.26644843623465</v>
+        <v>-7.886335689332415</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.310661566508429</v>
       </c>
       <c r="E71">
-        <v>-10.77038024782171</v>
+        <v>-8.910173508276305</v>
       </c>
       <c r="F71">
-        <v>5.260895786907331</v>
+        <v>5.120419586005785</v>
       </c>
       <c r="G71">
-        <v>-10.44101976184073</v>
+        <v>-8.354160234103187</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.529437083962032</v>
       </c>
       <c r="E72">
-        <v>-10.26977707399483</v>
+        <v>-8.662554895878703</v>
       </c>
       <c r="F72">
-        <v>6.352912653200252</v>
+        <v>4.964247479555994</v>
       </c>
       <c r="G72">
-        <v>-9.659309310997291</v>
+        <v>-8.613317101312344</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.741863389456103</v>
       </c>
       <c r="E73">
-        <v>-9.338365442654803</v>
+        <v>-8.884747548545706</v>
       </c>
       <c r="F73">
-        <v>5.245254553607671</v>
+        <v>5.152132803654561</v>
       </c>
       <c r="G73">
-        <v>-10.44261492678589</v>
+        <v>-7.890378427331754</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.941748545666085</v>
       </c>
       <c r="E74">
-        <v>-11.9871424164454</v>
+        <v>-8.533680748469273</v>
       </c>
       <c r="F74">
-        <v>5.331174477360841</v>
+        <v>5.316050145320528</v>
       </c>
       <c r="G74">
-        <v>-10.84852305283382</v>
+        <v>-7.939510029791915</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.132117528883027</v>
       </c>
       <c r="E75">
-        <v>-13.05075907067737</v>
+        <v>-8.670607972637546</v>
       </c>
       <c r="F75">
-        <v>5.24247289586907</v>
+        <v>4.884010156186029</v>
       </c>
       <c r="G75">
-        <v>-10.2614096715782</v>
+        <v>-8.128608871270842</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.308742320936185</v>
       </c>
       <c r="E76">
-        <v>-11.72179374490211</v>
+        <v>-9.156068537974104</v>
       </c>
       <c r="F76">
-        <v>5.906319905533372</v>
+        <v>5.091680207333059</v>
       </c>
       <c r="G76">
-        <v>-11.39480438868444</v>
+        <v>-7.679845372759788</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.469215097876774</v>
       </c>
       <c r="E77">
-        <v>-12.80813261829221</v>
+        <v>-9.554656382029224</v>
       </c>
       <c r="F77">
-        <v>5.10349272649698</v>
+        <v>5.136281165034591</v>
       </c>
       <c r="G77">
-        <v>-10.39868262217894</v>
+        <v>-7.691010222003683</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.613741365796256</v>
       </c>
       <c r="E78">
-        <v>-14.58741818838465</v>
+        <v>-9.884342450205438</v>
       </c>
       <c r="F78">
-        <v>5.853653962798185</v>
+        <v>5.154828311183271</v>
       </c>
       <c r="G78">
-        <v>-10.06150756898125</v>
+        <v>-7.370936851250081</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.734250804234884</v>
       </c>
       <c r="E79">
-        <v>-13.28323507458465</v>
+        <v>-11.1496431995824</v>
       </c>
       <c r="F79">
-        <v>5.623379421963561</v>
+        <v>5.026828980102692</v>
       </c>
       <c r="G79">
-        <v>-10.30867720240031</v>
+        <v>-7.381204909726931</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.833183804592769</v>
       </c>
       <c r="E80">
-        <v>-14.95256022164093</v>
+        <v>-11.01340125528273</v>
       </c>
       <c r="F80">
-        <v>5.854445882035261</v>
+        <v>4.934431223259629</v>
       </c>
       <c r="G80">
-        <v>-10.14296149485169</v>
+        <v>-7.174875153946656</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.896294673096738</v>
       </c>
       <c r="E81">
-        <v>-14.23991484362493</v>
+        <v>-11.94511607104946</v>
       </c>
       <c r="F81">
-        <v>4.653936080262883</v>
+        <v>5.235378757431495</v>
       </c>
       <c r="G81">
-        <v>-10.15540038745605</v>
+        <v>-6.933537923944144</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.92459100563843</v>
       </c>
       <c r="E82">
-        <v>-15.56140854222682</v>
+        <v>-12.37925540404511</v>
       </c>
       <c r="F82">
-        <v>5.926253738714339</v>
+        <v>4.959721280067098</v>
       </c>
       <c r="G82">
-        <v>-9.107585878046502</v>
+        <v>-7.482749820598281</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.901447750100941</v>
       </c>
       <c r="E83">
-        <v>-17.04130156754635</v>
+        <v>-13.21502273178566</v>
       </c>
       <c r="F83">
-        <v>5.401087029422314</v>
+        <v>4.715770393412255</v>
       </c>
       <c r="G83">
-        <v>-9.848912026182301</v>
+        <v>-6.572145603919287</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.825478195974524</v>
       </c>
       <c r="E84">
-        <v>-17.65436124441561</v>
+        <v>-13.91884253573641</v>
       </c>
       <c r="F84">
-        <v>6.161857995418575</v>
+        <v>4.847164374109507</v>
       </c>
       <c r="G84">
-        <v>-9.303655407583701</v>
+        <v>-6.253123057863609</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.685107085232859</v>
       </c>
       <c r="E85">
-        <v>-17.23154771870277</v>
+        <v>-15.49707945201655</v>
       </c>
       <c r="F85">
-        <v>5.702006399102485</v>
+        <v>5.049759846546988</v>
       </c>
       <c r="G85">
-        <v>-9.447858579701547</v>
+        <v>-6.644374463777027</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.47836410597885</v>
       </c>
       <c r="E86">
-        <v>-19.45614060704333</v>
+        <v>-15.81126988873983</v>
       </c>
       <c r="F86">
-        <v>4.953286522082152</v>
+        <v>4.758842184888218</v>
       </c>
       <c r="G86">
-        <v>-9.435089427906412</v>
+        <v>-6.80701340882502</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.204811818188343</v>
       </c>
       <c r="E87">
-        <v>-20.19650036422992</v>
+        <v>-16.81243055106902</v>
       </c>
       <c r="F87">
-        <v>4.643354515059523</v>
+        <v>4.709512906051508</v>
       </c>
       <c r="G87">
-        <v>-8.738356102759123</v>
+        <v>-5.904575601227029</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.866477365645366</v>
       </c>
       <c r="E88">
-        <v>-20.558481803668</v>
+        <v>-19.08683705603958</v>
       </c>
       <c r="F88">
-        <v>5.411343874603777</v>
+        <v>4.923864568669519</v>
       </c>
       <c r="G88">
-        <v>-9.201357296897813</v>
+        <v>-6.623624265766859</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.476101020328549</v>
       </c>
       <c r="E89">
-        <v>-24.27069269039227</v>
+        <v>-20.92455000304971</v>
       </c>
       <c r="F89">
-        <v>5.556573247662587</v>
+        <v>4.789372493885796</v>
       </c>
       <c r="G89">
-        <v>-8.397710064627548</v>
+        <v>-5.957876562799198</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.039620852746298</v>
       </c>
       <c r="E90">
-        <v>-25.11884489430346</v>
+        <v>-21.80277561016398</v>
       </c>
       <c r="F90">
-        <v>5.62069219810888</v>
+        <v>4.630594343586798</v>
       </c>
       <c r="G90">
-        <v>-8.380680177659716</v>
+        <v>-6.055761209753808</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.577782174780578</v>
       </c>
       <c r="E91">
-        <v>-27.46940883533739</v>
+        <v>-23.40606054394417</v>
       </c>
       <c r="F91">
-        <v>5.044363861285151</v>
+        <v>4.864947765512807</v>
       </c>
       <c r="G91">
-        <v>-9.236778574137743</v>
+        <v>-5.667922047020975</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.096056731861784</v>
       </c>
       <c r="E92">
-        <v>-26.64836464174336</v>
+        <v>-25.43711793775904</v>
       </c>
       <c r="F92">
-        <v>4.860444760311188</v>
+        <v>4.733167765605851</v>
       </c>
       <c r="G92">
-        <v>-8.542958839954135</v>
+        <v>-5.920908419389034</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.613431700380599</v>
       </c>
       <c r="E93">
-        <v>-30.56246728417888</v>
+        <v>-27.14407117941828</v>
       </c>
       <c r="F93">
-        <v>4.928495142451168</v>
+        <v>4.369830912124737</v>
       </c>
       <c r="G93">
-        <v>-7.454838350174689</v>
+        <v>-5.883697476731896</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.132112377594669</v>
       </c>
       <c r="E94">
-        <v>-30.47573992529381</v>
+        <v>-29.18648760620656</v>
       </c>
       <c r="F94">
-        <v>4.785846962219482</v>
+        <v>4.333627943152787</v>
       </c>
       <c r="G94">
-        <v>-8.679806239186521</v>
+        <v>-5.165486861205814</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.660276304983389</v>
       </c>
       <c r="E95">
-        <v>-35.20830761709063</v>
+        <v>-31.7901067132623</v>
       </c>
       <c r="F95">
-        <v>4.997289398518862</v>
+        <v>4.132772042261185</v>
       </c>
       <c r="G95">
-        <v>-7.867161075682984</v>
+        <v>-5.915666044250078</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.191720404704569</v>
       </c>
       <c r="E96">
-        <v>-37.21747758722366</v>
+        <v>-33.95315939279721</v>
       </c>
       <c r="F96">
-        <v>4.63170435590655</v>
+        <v>3.734537726834934</v>
       </c>
       <c r="G96">
-        <v>-8.222077443749583</v>
+        <v>-5.548235071985976</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.724830819704893</v>
       </c>
       <c r="E97">
-        <v>-39.3096930944023</v>
+        <v>-36.3311739840826</v>
       </c>
       <c r="F97">
-        <v>4.915181621553375</v>
+        <v>3.567195914325795</v>
       </c>
       <c r="G97">
-        <v>-8.2037408791139</v>
+        <v>-5.916169917956164</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.246245794871048</v>
       </c>
       <c r="E98">
-        <v>-40.53027414083918</v>
+        <v>-38.51073152542239</v>
       </c>
       <c r="F98">
-        <v>4.469930829079029</v>
+        <v>3.184178708088971</v>
       </c>
       <c r="G98">
-        <v>-6.849396236517154</v>
+        <v>-5.825856430315781</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.758787740779317</v>
       </c>
       <c r="E99">
-        <v>-44.34163464152108</v>
+        <v>-41.21097924716158</v>
       </c>
       <c r="F99">
-        <v>3.974502509547506</v>
+        <v>3.387330843421132</v>
       </c>
       <c r="G99">
-        <v>-8.906166932842112</v>
+        <v>-6.116199947038081</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.246573205614627</v>
       </c>
       <c r="E100">
-        <v>-45.68561174962993</v>
+        <v>-45.21313619950045</v>
       </c>
       <c r="F100">
-        <v>4.407743631416064</v>
+        <v>3.038342970091312</v>
       </c>
       <c r="G100">
-        <v>-8.28903129416098</v>
+        <v>-6.501015867534406</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.73845802015102</v>
       </c>
       <c r="E101">
-        <v>-47.48684496496843</v>
+        <v>-46.68527621757936</v>
       </c>
       <c r="F101">
-        <v>3.185802308198458</v>
+        <v>2.341379488397892</v>
       </c>
       <c r="G101">
-        <v>-8.461376987598731</v>
+        <v>-6.186123519421868</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.199122015089888</v>
       </c>
       <c r="E102">
-        <v>-49.41723474608645</v>
+        <v>-48.52495155694047</v>
       </c>
       <c r="F102">
-        <v>3.425556685590719</v>
+        <v>2.17613178868303</v>
       </c>
       <c r="G102">
-        <v>-9.06947683925002</v>
+        <v>-5.874478937580675</v>
       </c>
     </row>
   </sheetData>
